--- a/output/bond_dataset.xlsx
+++ b/output/bond_dataset.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bonds'!$A$1:$AF$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bonds'!$A$1:$AF$111</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Excluded'!$A$1:$B$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF110"/>
+  <dimension ref="A1:AF111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -14201,8 +14201,128 @@
       </c>
       <c r="AF110" t="inlineStr"/>
     </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Trinity Capital Inc.</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="H111" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>48228</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>48197</v>
+      </c>
+      <c r="L111" s="5" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="M111" s="5" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>5y</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>UST 5.000% due September 30, 2031</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>UST</t>
+        </is>
+      </c>
+      <c r="Q111" s="5" t="n">
+        <v>262.5</v>
+      </c>
+      <c r="R111" s="4" t="n">
+        <v>7.714</v>
+      </c>
+      <c r="S111" s="4" t="n">
+        <v>99.104</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Baa3</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr"/>
+      <c r="V111" t="inlineStr"/>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>BBB-</t>
+        </is>
+      </c>
+      <c r="X111" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>IG</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>senior unsecured</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>Keefe, Bruyette &amp; Woods, Inc.; MUFG Securities Americas Inc.</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr"/>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Spread to Benchmark Treasury: + 262.5 basis points; Benchmark Treasury: 5.000% due September 30, 2031</t>
+        </is>
+      </c>
+      <c r="AD111" t="inlineStr">
+        <is>
+          <t>2026-09-30_trinity-capital-inc_0001213900-26-105335.txt</t>
+        </is>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1786108/000121390026105335/ea0307219-02_fwp.htm</t>
+        </is>
+      </c>
+      <c r="AF111" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AF110"/>
+  <autoFilter ref="A1:AF111"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
